--- a/data/trans_orig/P33_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>212399</t>
+          <t>211997</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236996</t>
+          <t>236636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>204976</t>
+          <t>203958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228650</t>
+          <t>228506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>423236</t>
+          <t>423132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>458482</t>
+          <t>457477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>32021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56258</t>
+          <t>56660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29308</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52982</t>
+          <t>54000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68133</t>
+          <t>69138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103379</t>
+          <t>103483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>357742</t>
+          <t>358723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>396453</t>
+          <t>394779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>308165</t>
+          <t>308115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>352658</t>
+          <t>350292</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>679796</t>
+          <t>674932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>734624</t>
+          <t>734757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96622</t>
+          <t>98296</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>135333</t>
+          <t>134352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149353</t>
+          <t>151719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>193846</t>
+          <t>193896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260462</t>
+          <t>260329</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315290</t>
+          <t>320154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>259053</t>
+          <t>259821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>284440</t>
+          <t>285577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>247459</t>
+          <t>248308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>277919</t>
+          <t>278540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>518305</t>
+          <t>518508</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>555510</t>
+          <t>555730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>28411</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54935</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53541</t>
+          <t>52920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84001</t>
+          <t>83152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89939</t>
+          <t>89719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127144</t>
+          <t>126941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>288491</t>
+          <t>289878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314709</t>
+          <t>314899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>286978</t>
+          <t>287588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>316662</t>
+          <t>316464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>585014</t>
+          <t>585352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>625608</t>
+          <t>626545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>34145</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60553</t>
+          <t>59166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54794</t>
+          <t>54992</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>83868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94892</t>
+          <t>93955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135486</t>
+          <t>135148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139201</t>
+          <t>138556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163799</t>
+          <t>163062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131805</t>
+          <t>131740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158337</t>
+          <t>158541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>278741</t>
+          <t>280091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>313242</t>
+          <t>314480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39509</t>
+          <t>40246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64107</t>
+          <t>64752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48337</t>
+          <t>48133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74869</t>
+          <t>74934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96740</t>
+          <t>95502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131241</t>
+          <t>129891</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214468</t>
+          <t>212866</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>236976</t>
+          <t>236948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>196525</t>
+          <t>195633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>224715</t>
+          <t>223502</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>417379</t>
+          <t>418345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>455039</t>
+          <t>454256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31901</t>
+          <t>31929</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54409</t>
+          <t>56011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51445</t>
+          <t>52658</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79635</t>
+          <t>80527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89999</t>
+          <t>90782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127659</t>
+          <t>126693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>490963</t>
+          <t>492980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>529472</t>
+          <t>529321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>465373</t>
+          <t>462149</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>509824</t>
+          <t>506839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>970954</t>
+          <t>968033</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1025585</t>
+          <t>1027350</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76499</t>
+          <t>76650</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115008</t>
+          <t>112991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125001</t>
+          <t>127986</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>169452</t>
+          <t>172676</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215211</t>
+          <t>213446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>269842</t>
+          <t>272763</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>537793</t>
+          <t>540919</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>583531</t>
+          <t>583917</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>566786</t>
+          <t>565650</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>614967</t>
+          <t>615970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1118586</t>
+          <t>1119711</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1184821</t>
+          <t>1185839</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143154</t>
+          <t>142768</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>188892</t>
+          <t>185766</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161626</t>
+          <t>160623</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>209807</t>
+          <t>210943</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318457</t>
+          <t>317439</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384692</t>
+          <t>383567</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2588708</t>
+          <t>2582930</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2674029</t>
+          <t>2674378</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2501367</t>
+          <t>2498276</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2598566</t>
+          <t>2596209</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5118185</t>
+          <t>5112156</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5248700</t>
+          <t>5243770</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>555576</t>
+          <t>555227</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>640897</t>
+          <t>646675</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>758572</t>
+          <t>760929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>855771</t>
+          <t>858862</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1338043</t>
+          <t>1342973</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1468558</t>
+          <t>1474587</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>200256</t>
+          <t>201282</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231375</t>
+          <t>232380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>165634</t>
+          <t>165805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>200775</t>
+          <t>201010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>373852</t>
+          <t>374778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>422557</t>
+          <t>420731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62055</t>
+          <t>61050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93174</t>
+          <t>92148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85488</t>
+          <t>85253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120629</t>
+          <t>120458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157136</t>
+          <t>158962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205841</t>
+          <t>204915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>340316</t>
+          <t>340616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>384147</t>
+          <t>382092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>317016</t>
+          <t>315613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>362821</t>
+          <t>362562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>669559</t>
+          <t>668299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>731984</t>
+          <t>730566</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118306</t>
+          <t>120361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162137</t>
+          <t>161837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160944</t>
+          <t>161203</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>206749</t>
+          <t>208152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>294234</t>
+          <t>295652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>356659</t>
+          <t>357919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>207407</t>
+          <t>207277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>240547</t>
+          <t>241457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211539</t>
+          <t>210515</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248624</t>
+          <t>246691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>429532</t>
+          <t>430706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>478692</t>
+          <t>478998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80493</t>
+          <t>79583</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113633</t>
+          <t>113763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92396</t>
+          <t>94329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129481</t>
+          <t>130505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183368</t>
+          <t>183062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232528</t>
+          <t>231354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>235540</t>
+          <t>235716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273537</t>
+          <t>273510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>192740</t>
+          <t>193246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232629</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>441847</t>
+          <t>441257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497942</t>
+          <t>494714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100445</t>
+          <t>100472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138442</t>
+          <t>138266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155150</t>
+          <t>152764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>195039</t>
+          <t>194533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263819</t>
+          <t>267047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319914</t>
+          <t>320504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130489</t>
+          <t>131825</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158365</t>
+          <t>159737</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117381</t>
+          <t>115820</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146671</t>
+          <t>145083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257684</t>
+          <t>255272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>296724</t>
+          <t>294525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>52881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82129</t>
+          <t>80793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72029</t>
+          <t>73617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101319</t>
+          <t>102880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134594</t>
+          <t>136793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173634</t>
+          <t>176046</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190217</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>220050</t>
+          <t>217443</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>184833</t>
+          <t>184877</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>214725</t>
+          <t>213509</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>382731</t>
+          <t>385169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>425644</t>
+          <t>426625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53931</t>
+          <t>56538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83764</t>
+          <t>82952</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>66522</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95198</t>
+          <t>95154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128368</t>
+          <t>127387</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>171281</t>
+          <t>168843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>496013</t>
+          <t>498279</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>539104</t>
+          <t>542101</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>466771</t>
+          <t>468072</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>518003</t>
+          <t>516561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>980081</t>
+          <t>978369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1043860</t>
+          <t>1045800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>120774</t>
+          <t>117777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>163865</t>
+          <t>161599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>174589</t>
+          <t>176031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>225821</t>
+          <t>224520</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>308610</t>
+          <t>306670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>372389</t>
+          <t>374101</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>575262</t>
+          <t>575726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>623898</t>
+          <t>622140</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>575126</t>
+          <t>575865</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>629671</t>
+          <t>629636</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1168604</t>
+          <t>1167066</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1239680</t>
+          <t>1239015</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152279</t>
+          <t>154037</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>200915</t>
+          <t>200451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>189137</t>
+          <t>189172</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>243682</t>
+          <t>242943</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>355305</t>
+          <t>355970</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>426381</t>
+          <t>427919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2477335</t>
+          <t>2471615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2580460</t>
+          <t>2581173</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2340558</t>
+          <t>2329295</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2457196</t>
+          <t>2449801</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4842118</t>
+          <t>4851463</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5001553</t>
+          <t>5009745</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>833100</t>
+          <t>832387</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>936225</t>
+          <t>941945</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1091762</t>
+          <t>1099157</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1208400</t>
+          <t>1219663</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1960964</t>
+          <t>1952772</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2120399</t>
+          <t>2111054</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>179682</t>
+          <t>177800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214591</t>
+          <t>212398</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163671</t>
+          <t>163123</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198047</t>
+          <t>195555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>351565</t>
+          <t>351059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>397624</t>
+          <t>398071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77583</t>
+          <t>79776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112492</t>
+          <t>114374</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85435</t>
+          <t>87927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119811</t>
+          <t>120359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178032</t>
+          <t>177585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224091</t>
+          <t>224597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>349000</t>
+          <t>347126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>389185</t>
+          <t>388001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>306595</t>
+          <t>308138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>353169</t>
+          <t>352301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>666340</t>
+          <t>671110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>729930</t>
+          <t>731636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113390</t>
+          <t>114574</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153575</t>
+          <t>155449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169915</t>
+          <t>170783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216489</t>
+          <t>214946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295729</t>
+          <t>294023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359319</t>
+          <t>354549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>265349</t>
+          <t>265953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>289084</t>
+          <t>289332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>245820</t>
+          <t>248424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>277760</t>
+          <t>277722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>521355</t>
+          <t>520510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>561124</t>
+          <t>559805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29481</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53216</t>
+          <t>52612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58549</t>
+          <t>58587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90489</t>
+          <t>87885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93750</t>
+          <t>95069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133519</t>
+          <t>134364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223924</t>
+          <t>224455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>260212</t>
+          <t>261723</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202150</t>
+          <t>201919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241092</t>
+          <t>241605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>438330</t>
+          <t>436389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>490752</t>
+          <t>492174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108939</t>
+          <t>107428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>145227</t>
+          <t>144696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140870</t>
+          <t>140357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179812</t>
+          <t>180043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260361</t>
+          <t>258939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312783</t>
+          <t>314724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>186000</t>
+          <t>186391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>201012</t>
+          <t>202026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190514</t>
+          <t>190244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207074</t>
+          <t>207189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>383429</t>
+          <t>381857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>405883</t>
+          <t>404512</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>28343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>25296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46379</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>196935</t>
+          <t>196611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>222809</t>
+          <t>222179</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>174172</t>
+          <t>171026</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>204922</t>
+          <t>203275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>377580</t>
+          <t>377726</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>417536</t>
+          <t>418810</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>40944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66188</t>
+          <t>66512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67228</t>
+          <t>68875</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97978</t>
+          <t>101124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117737</t>
+          <t>116463</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157693</t>
+          <t>157547</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>450532</t>
+          <t>452585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>498889</t>
+          <t>500156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>456250</t>
+          <t>454279</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>505347</t>
+          <t>504693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>922957</t>
+          <t>921821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>991570</t>
+          <t>990277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153302</t>
+          <t>152035</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201659</t>
+          <t>199606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>183994</t>
+          <t>184648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>233091</t>
+          <t>235062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>349962</t>
+          <t>351255</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>418575</t>
+          <t>419711</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>609122</t>
+          <t>608511</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>651882</t>
+          <t>652810</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>632661</t>
+          <t>629364</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>681719</t>
+          <t>679922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1257063</t>
+          <t>1257997</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1323839</t>
+          <t>1321584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126701</t>
+          <t>125773</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>169461</t>
+          <t>170072</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>143368</t>
+          <t>145165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>192426</t>
+          <t>195723</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279831</t>
+          <t>282086</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>346607</t>
+          <t>345673</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2552237</t>
+          <t>2552675</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2652505</t>
+          <t>2658807</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2468587</t>
+          <t>2467351</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2581803</t>
+          <t>2578401</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5053561</t>
+          <t>5045986</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5198847</t>
+          <t>5198786</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>735079</t>
+          <t>728777</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>835347</t>
+          <t>834909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>948199</t>
+          <t>951601</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1061415</t>
+          <t>1062651</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1718740</t>
+          <t>1718801</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1864026</t>
+          <t>1871601</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023</t>
+          <t>Población que duerme las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>194533</t>
+          <t>195838</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232419</t>
+          <t>232916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173617</t>
+          <t>173594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>200990</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382172</t>
+          <t>380013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>427435</t>
+          <t>425499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79024</t>
+          <t>78527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116910</t>
+          <t>115605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88645</t>
+          <t>89210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116018</t>
+          <t>116041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173642</t>
+          <t>175578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218905</t>
+          <t>221064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>279926</t>
+          <t>280408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>327052</t>
+          <t>325410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289539</t>
+          <t>288976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>321816</t>
+          <t>321396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>581524</t>
+          <t>581425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>641057</t>
+          <t>637920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,69%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96169</t>
+          <t>97811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143295</t>
+          <t>142813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120603</t>
+          <t>121023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>152880</t>
+          <t>153443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>224583</t>
+          <t>227720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284116</t>
+          <t>284215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>214931</t>
+          <t>215587</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244254</t>
+          <t>246464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>220589</t>
+          <t>222131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249984</t>
+          <t>251039</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>446763</t>
+          <t>448155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>487785</t>
+          <t>488707</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,13%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69338</t>
+          <t>67128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98661</t>
+          <t>98005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95702</t>
+          <t>94647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125097</t>
+          <t>123555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>171493</t>
+          <t>170571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212515</t>
+          <t>211123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206577</t>
+          <t>204675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242800</t>
+          <t>240862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>280079</t>
+          <t>278715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>374041</t>
+          <t>367960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>503237</t>
+          <t>505951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>601571</t>
+          <t>603489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64446</t>
+          <t>66384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100669</t>
+          <t>102571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82958</t>
+          <t>89039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176920</t>
+          <t>178284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162674</t>
+          <t>160756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261008</t>
+          <t>258294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106829</t>
+          <t>106205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127361</t>
+          <t>127317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105433</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124261</t>
+          <t>123666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>215738</t>
+          <t>217912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245865</t>
+          <t>246099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51381</t>
+          <t>51425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71913</t>
+          <t>72537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84067</t>
+          <t>84662</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102895</t>
+          <t>102788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141205</t>
+          <t>140971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171332</t>
+          <t>169158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>194730</t>
+          <t>195366</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>217733</t>
+          <t>217449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>153920</t>
+          <t>154725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177656</t>
+          <t>178523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>357715</t>
+          <t>358570</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>390930</t>
+          <t>392087</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74906</t>
+          <t>74270</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79051</t>
+          <t>78184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102787</t>
+          <t>101982</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>135413</t>
+          <t>134256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>168628</t>
+          <t>167773</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>398999</t>
+          <t>402778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>453872</t>
+          <t>455736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>197265</t>
+          <t>208317</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>544324</t>
+          <t>546017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>541304</t>
+          <t>531127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>981193</t>
+          <t>983527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170407</t>
+          <t>168543</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>225280</t>
+          <t>221501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>300011</t>
+          <t>298318</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>647070</t>
+          <t>636018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>487421</t>
+          <t>485087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>927310</t>
+          <t>937487</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,83%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>815951</t>
+          <t>814189</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>895839</t>
+          <t>889794</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>596701</t>
+          <t>598248</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>628918</t>
+          <t>628514</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1424489</t>
+          <t>1422396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1531373</t>
+          <t>1530725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32881</t>
+          <t>38926</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112769</t>
+          <t>114531</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85423</t>
+          <t>85827</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>117640</t>
+          <t>116093</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111689</t>
+          <t>112337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>218573</t>
+          <t>220666</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2503236</t>
+          <t>2493003</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2771638</t>
+          <t>2764034</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1916101</t>
+          <t>1893941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2514675</t>
+          <t>2510660</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4492493</t>
+          <t>4450941</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5138820</t>
+          <t>5157772</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>585241</t>
+          <t>592845</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>853643</t>
+          <t>863876</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1043775</t>
+          <t>1047790</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1642349</t>
+          <t>1664509</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1776509</t>
+          <t>1757557</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2422836</t>
+          <t>2464388</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>211997</t>
+          <t>211560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236636</t>
+          <t>235882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>203958</t>
+          <t>202889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228506</t>
+          <t>227585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>423132</t>
+          <t>423833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>457477</t>
+          <t>459465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32021</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56660</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29452</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54000</t>
+          <t>55069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69138</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103483</t>
+          <t>102782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>358723</t>
+          <t>358078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>394779</t>
+          <t>395383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>308115</t>
+          <t>309501</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>350292</t>
+          <t>351764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>674932</t>
+          <t>678585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>734757</t>
+          <t>734866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98296</t>
+          <t>97692</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134352</t>
+          <t>134997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151719</t>
+          <t>150247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>193896</t>
+          <t>192510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260329</t>
+          <t>260220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320154</t>
+          <t>316501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>259821</t>
+          <t>259660</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>285577</t>
+          <t>285666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>248308</t>
+          <t>247849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>278540</t>
+          <t>277827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>518508</t>
+          <t>518383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>555730</t>
+          <t>554616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>28322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52920</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83152</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89719</t>
+          <t>90833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126941</t>
+          <t>127066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>289878</t>
+          <t>289233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314899</t>
+          <t>315649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>287588</t>
+          <t>288576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>316464</t>
+          <t>317975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>585352</t>
+          <t>585649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>626545</t>
+          <t>624965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34145</t>
+          <t>33395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59166</t>
+          <t>59811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54992</t>
+          <t>53481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83868</t>
+          <t>82880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93955</t>
+          <t>95535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135148</t>
+          <t>134851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>138556</t>
+          <t>138504</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163062</t>
+          <t>163203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131740</t>
+          <t>131096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158541</t>
+          <t>158850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>280091</t>
+          <t>279272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>314480</t>
+          <t>315739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40246</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>64804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48133</t>
+          <t>47824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74934</t>
+          <t>75578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95502</t>
+          <t>94243</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129891</t>
+          <t>130710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>212866</t>
+          <t>213184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>236948</t>
+          <t>236934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>195633</t>
+          <t>195542</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>223502</t>
+          <t>223338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>418345</t>
+          <t>416090</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>454256</t>
+          <t>454247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31929</t>
+          <t>31943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56011</t>
+          <t>55693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>52822</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80527</t>
+          <t>80618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90782</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126693</t>
+          <t>128948</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>492980</t>
+          <t>491661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>529321</t>
+          <t>529488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>462149</t>
+          <t>463490</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>506839</t>
+          <t>504926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>968033</t>
+          <t>970208</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1027350</t>
+          <t>1027901</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76650</t>
+          <t>76483</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112991</t>
+          <t>114310</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127986</t>
+          <t>129899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>172676</t>
+          <t>171335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213446</t>
+          <t>212895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>272763</t>
+          <t>270588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>540919</t>
+          <t>537641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>583917</t>
+          <t>583412</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>565650</t>
+          <t>565094</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>615970</t>
+          <t>615181</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1119711</t>
+          <t>1117533</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1185839</t>
+          <t>1184224</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142768</t>
+          <t>143273</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>185766</t>
+          <t>189044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160623</t>
+          <t>161412</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>210943</t>
+          <t>211499</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317439</t>
+          <t>319054</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>383567</t>
+          <t>385745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2582930</t>
+          <t>2579842</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2674378</t>
+          <t>2675558</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2498276</t>
+          <t>2496057</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2596209</t>
+          <t>2595772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5112156</t>
+          <t>5117800</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5243770</t>
+          <t>5248057</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>555227</t>
+          <t>554047</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>646675</t>
+          <t>649763</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>760929</t>
+          <t>761366</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>858862</t>
+          <t>861081</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1342973</t>
+          <t>1338686</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1474587</t>
+          <t>1468943</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>201282</t>
+          <t>200876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232380</t>
+          <t>231406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>165805</t>
+          <t>166982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>201010</t>
+          <t>200135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>374778</t>
+          <t>376794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>420731</t>
+          <t>422855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61050</t>
+          <t>62024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92148</t>
+          <t>92554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85253</t>
+          <t>86128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120458</t>
+          <t>119281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158962</t>
+          <t>156838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204915</t>
+          <t>202899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>340616</t>
+          <t>340751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>382092</t>
+          <t>384638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>315613</t>
+          <t>315481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>362562</t>
+          <t>361717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>668299</t>
+          <t>671819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>730566</t>
+          <t>733697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120361</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161837</t>
+          <t>161702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161203</t>
+          <t>162048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208152</t>
+          <t>208284</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295652</t>
+          <t>292521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>357919</t>
+          <t>354399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>207277</t>
+          <t>206972</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241457</t>
+          <t>240560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210515</t>
+          <t>213662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246691</t>
+          <t>248171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>430706</t>
+          <t>431586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>478998</t>
+          <t>480530</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79583</t>
+          <t>80480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113763</t>
+          <t>114068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94329</t>
+          <t>92849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130505</t>
+          <t>127358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183062</t>
+          <t>181530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231354</t>
+          <t>230474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>235716</t>
+          <t>235173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273510</t>
+          <t>272444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>193246</t>
+          <t>194834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>235015</t>
+          <t>237420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>441257</t>
+          <t>440936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>494714</t>
+          <t>496361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100472</t>
+          <t>101538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138266</t>
+          <t>138809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152764</t>
+          <t>150359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194533</t>
+          <t>192945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>267047</t>
+          <t>265400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>320504</t>
+          <t>320825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131825</t>
+          <t>132066</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159737</t>
+          <t>159632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115820</t>
+          <t>116393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145083</t>
+          <t>144778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255272</t>
+          <t>254889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294525</t>
+          <t>296750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52881</t>
+          <t>52986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80793</t>
+          <t>80552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73617</t>
+          <t>73922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102880</t>
+          <t>102307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136793</t>
+          <t>134568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176046</t>
+          <t>176429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>191029</t>
+          <t>189345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>217443</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>184877</t>
+          <t>186134</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>213509</t>
+          <t>215315</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>385169</t>
+          <t>384000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>426625</t>
+          <t>425922</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56538</t>
+          <t>55859</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82952</t>
+          <t>84636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66522</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95154</t>
+          <t>93897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127387</t>
+          <t>128090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>168843</t>
+          <t>170012</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>498279</t>
+          <t>494861</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>542101</t>
+          <t>539726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>468072</t>
+          <t>465440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>516561</t>
+          <t>517543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>978369</t>
+          <t>976592</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1045800</t>
+          <t>1042523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117777</t>
+          <t>120152</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>161599</t>
+          <t>165017</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>176031</t>
+          <t>175049</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>224520</t>
+          <t>227152</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>306670</t>
+          <t>309947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>374101</t>
+          <t>375878</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>575726</t>
+          <t>571756</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>622140</t>
+          <t>622390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>575865</t>
+          <t>575559</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>629636</t>
+          <t>629476</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1167066</t>
+          <t>1167790</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1239015</t>
+          <t>1235524</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154037</t>
+          <t>153787</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>200451</t>
+          <t>204421</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>189172</t>
+          <t>189332</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>242943</t>
+          <t>243249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>355970</t>
+          <t>359461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>427919</t>
+          <t>427195</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2471615</t>
+          <t>2478624</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2581173</t>
+          <t>2587028</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2329295</t>
+          <t>2332575</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2449801</t>
+          <t>2454347</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4851463</t>
+          <t>4842440</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5009745</t>
+          <t>4994265</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>832387</t>
+          <t>826532</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>941945</t>
+          <t>934936</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1099157</t>
+          <t>1094611</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1219663</t>
+          <t>1216383</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1952772</t>
+          <t>1968252</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2111054</t>
+          <t>2120077</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>177800</t>
+          <t>175607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>212398</t>
+          <t>210764</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163123</t>
+          <t>161171</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195555</t>
+          <t>194358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>351059</t>
+          <t>354430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398071</t>
+          <t>401211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,7%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79776</t>
+          <t>81410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114374</t>
+          <t>116567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87927</t>
+          <t>89124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120359</t>
+          <t>122311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177585</t>
+          <t>174445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224597</t>
+          <t>221226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>347126</t>
+          <t>348955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>388001</t>
+          <t>389215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>308138</t>
+          <t>308735</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>352301</t>
+          <t>353051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>671110</t>
+          <t>667233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>731636</t>
+          <t>728540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114574</t>
+          <t>113360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155449</t>
+          <t>153620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170783</t>
+          <t>170033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>214946</t>
+          <t>214349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>294023</t>
+          <t>297119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>354549</t>
+          <t>358426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>265953</t>
+          <t>265062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>289332</t>
+          <t>287844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>248424</t>
+          <t>248648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>277722</t>
+          <t>278427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>520510</t>
+          <t>520052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>559805</t>
+          <t>557222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29233</t>
+          <t>30721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52612</t>
+          <t>53503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58587</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87885</t>
+          <t>87661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95069</t>
+          <t>97652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>134364</t>
+          <t>134822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>224455</t>
+          <t>223473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>261723</t>
+          <t>260883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201919</t>
+          <t>201512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241605</t>
+          <t>241780</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>436389</t>
+          <t>435765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>492174</t>
+          <t>491086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107428</t>
+          <t>108268</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144696</t>
+          <t>145678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140357</t>
+          <t>140182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180043</t>
+          <t>180450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258939</t>
+          <t>260027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314724</t>
+          <t>315348</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>186391</t>
+          <t>185351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>202026</t>
+          <t>201674</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190244</t>
+          <t>191019</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207189</t>
+          <t>207587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>381857</t>
+          <t>381866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>404512</t>
+          <t>405451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25296</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47951</t>
+          <t>47942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>196611</t>
+          <t>196831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>222179</t>
+          <t>221900</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>171026</t>
+          <t>173210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>203275</t>
+          <t>202244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>377726</t>
+          <t>376330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>418810</t>
+          <t>419452</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40944</t>
+          <t>41223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66512</t>
+          <t>66292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68875</t>
+          <t>69906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101124</t>
+          <t>98940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116463</t>
+          <t>115821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>157547</t>
+          <t>158943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>452585</t>
+          <t>452658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>500156</t>
+          <t>500334</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>454279</t>
+          <t>453903</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>504693</t>
+          <t>503504</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>921821</t>
+          <t>924952</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>990277</t>
+          <t>991086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>152035</t>
+          <t>151857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199606</t>
+          <t>199533</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>184648</t>
+          <t>185837</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>235062</t>
+          <t>235438</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>351255</t>
+          <t>350446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>419711</t>
+          <t>416580</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>608511</t>
+          <t>606925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>652810</t>
+          <t>652091</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>629364</t>
+          <t>633145</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>679922</t>
+          <t>681683</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1257997</t>
+          <t>1256937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1321584</t>
+          <t>1323160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,51%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125773</t>
+          <t>126492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170072</t>
+          <t>171658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>145165</t>
+          <t>143404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>195723</t>
+          <t>191942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282086</t>
+          <t>280510</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>345673</t>
+          <t>346733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2552675</t>
+          <t>2549311</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2658807</t>
+          <t>2652481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2467351</t>
+          <t>2467735</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2578401</t>
+          <t>2577470</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5045986</t>
+          <t>5046798</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5198786</t>
+          <t>5201128</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>728777</t>
+          <t>735103</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>834909</t>
+          <t>838273</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>951601</t>
+          <t>952532</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1062651</t>
+          <t>1062267</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1718801</t>
+          <t>1716459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1871601</t>
+          <t>1870789</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>214561</t>
+          <t>220119</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>195838</t>
+          <t>202817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232916</t>
+          <t>235934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>209722</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173594</t>
+          <t>196343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>200425</t>
+          <t>223227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>402803</t>
+          <t>429841</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>380013</t>
+          <t>410243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>425499</t>
+          <t>452555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>96882</t>
+          <t>98726</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78527</t>
+          <t>82911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115605</t>
+          <t>116028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>101392</t>
+          <t>106339</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89210</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116041</t>
+          <t>119718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>198274</t>
+          <t>205065</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175578</t>
+          <t>182351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>221064</t>
+          <t>224663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>305594</t>
+          <t>315235</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>280408</t>
+          <t>293533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>325410</t>
+          <t>336898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>305678</t>
+          <t>323459</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>288976</t>
+          <t>306292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>321396</t>
+          <t>341653</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>611272</t>
+          <t>638694</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>581425</t>
+          <t>611208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>637920</t>
+          <t>668987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>117627</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97811</t>
+          <t>98240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142813</t>
+          <t>141605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>136741</t>
+          <t>146228</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121023</t>
+          <t>128034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>153443</t>
+          <t>163395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>254368</t>
+          <t>266131</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>227720</t>
+          <t>235838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284215</t>
+          <t>293617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423221</t>
+          <t>435138</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423221</t>
+          <t>435138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423221</t>
+          <t>435138</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>442419</t>
+          <t>469687</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>442419</t>
+          <t>469687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>442419</t>
+          <t>469687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>865640</t>
+          <t>904825</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>865640</t>
+          <t>904825</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>865640</t>
+          <t>904825</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>231649</t>
+          <t>228775</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>215587</t>
+          <t>212902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>246464</t>
+          <t>243544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>236741</t>
+          <t>240006</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>222131</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251039</t>
+          <t>254343</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>468390</t>
+          <t>468781</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>448155</t>
+          <t>447723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>488707</t>
+          <t>489507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81943</t>
+          <t>84812</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67128</t>
+          <t>70043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98005</t>
+          <t>100685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>108945</t>
+          <t>112231</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94647</t>
+          <t>97894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123555</t>
+          <t>125845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>190888</t>
+          <t>197043</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>170571</t>
+          <t>176317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211123</t>
+          <t>218101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>313592</t>
+          <t>313587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>313592</t>
+          <t>313587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313592</t>
+          <t>313587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>345686</t>
+          <t>352237</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>345686</t>
+          <t>352237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>345686</t>
+          <t>352237</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>659278</t>
+          <t>665824</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>659278</t>
+          <t>665824</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>659278</t>
+          <t>665824</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>225655</t>
+          <t>265262</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204675</t>
+          <t>242244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240862</t>
+          <t>284601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>317580</t>
+          <t>246009</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>278715</t>
+          <t>227915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>367960</t>
+          <t>264159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>543235</t>
+          <t>511270</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>505951</t>
+          <t>481088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>603489</t>
+          <t>539429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>81591</t>
+          <t>101522</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66384</t>
+          <t>82183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102571</t>
+          <t>124540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>139419</t>
+          <t>155799</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89039</t>
+          <t>137649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178284</t>
+          <t>173893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>221010</t>
+          <t>257322</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160756</t>
+          <t>229163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258294</t>
+          <t>287504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>307246</t>
+          <t>366784</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>307246</t>
+          <t>366784</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>307246</t>
+          <t>366784</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>456999</t>
+          <t>401808</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>456999</t>
+          <t>401808</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>456999</t>
+          <t>401808</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>764245</t>
+          <t>768592</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>764245</t>
+          <t>768592</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>764245</t>
+          <t>768592</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>117053</t>
+          <t>137830</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>126944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127317</t>
+          <t>149004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>114251</t>
+          <t>126092</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105540</t>
+          <t>116115</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123666</t>
+          <t>137218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>231304</t>
+          <t>263922</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>217912</t>
+          <t>247681</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>246099</t>
+          <t>278403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61689</t>
+          <t>67835</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>56661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72537</t>
+          <t>78721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>94077</t>
+          <t>100787</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84662</t>
+          <t>89661</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102788</t>
+          <t>110764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>155766</t>
+          <t>168622</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140971</t>
+          <t>154141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169158</t>
+          <t>184863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208328</t>
+          <t>226879</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208328</t>
+          <t>226879</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208328</t>
+          <t>226879</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387070</t>
+          <t>432544</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387070</t>
+          <t>432544</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387070</t>
+          <t>432544</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>207514</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195366</t>
+          <t>194061</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>217449</t>
+          <t>217766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>167077</t>
+          <t>170750</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>154725</t>
+          <t>158021</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178523</t>
+          <t>181580</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>374289</t>
+          <t>378264</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>358570</t>
+          <t>358355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>392087</t>
+          <t>393456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>62425</t>
+          <t>63193</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>52941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74270</t>
+          <t>76646</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>89630</t>
+          <t>92602</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78184</t>
+          <t>81772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101982</t>
+          <t>105331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>152054</t>
+          <t>155795</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134256</t>
+          <t>140603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>167773</t>
+          <t>175704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256707</t>
+          <t>263352</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256707</t>
+          <t>263352</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256707</t>
+          <t>263352</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526343</t>
+          <t>534059</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526343</t>
+          <t>534059</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526343</t>
+          <t>534059</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>430171</t>
+          <t>503739</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>402778</t>
+          <t>476573</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>455736</t>
+          <t>530339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>404265</t>
+          <t>483561</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208317</t>
+          <t>459521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>546017</t>
+          <t>509720</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>834436</t>
+          <t>987301</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>531127</t>
+          <t>949739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>983527</t>
+          <t>1026251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>194108</t>
+          <t>215948</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168543</t>
+          <t>189348</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>221501</t>
+          <t>243114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>440070</t>
+          <t>280607</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298318</t>
+          <t>254448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>636018</t>
+          <t>304647</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>634178</t>
+          <t>496555</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>485087</t>
+          <t>457605</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>937487</t>
+          <t>534117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>844335</t>
+          <t>764168</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>844335</t>
+          <t>764168</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>844335</t>
+          <t>764168</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1468614</t>
+          <t>1483856</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1468614</t>
+          <t>1483856</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1468614</t>
+          <t>1483856</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>850283</t>
+          <t>709765</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>814189</t>
+          <t>690928</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>889794</t>
+          <t>726290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>613619</t>
+          <t>710930</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>598248</t>
+          <t>690915</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>628514</t>
+          <t>728089</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1463903</t>
+          <t>1420695</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1422396</t>
+          <t>1395648</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1530725</t>
+          <t>1445370</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>78437</t>
+          <t>88307</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>71782</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114531</t>
+          <t>107144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>118480</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>85827</t>
+          <t>101321</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116093</t>
+          <t>138495</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>179159</t>
+          <t>206787</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112337</t>
+          <t>182112</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>220666</t>
+          <t>231834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714341</t>
+          <t>829410</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714341</t>
+          <t>829410</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714341</t>
+          <t>829410</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643062</t>
+          <t>1627482</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643062</t>
+          <t>1627482</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643062</t>
+          <t>1627482</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2582177</t>
+          <t>2588239</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2493003</t>
+          <t>2534456</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2764034</t>
+          <t>2641203</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2347455</t>
+          <t>2510528</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1893941</t>
+          <t>2453912</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2510660</t>
+          <t>2557005</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4929632</t>
+          <t>5098767</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4450941</t>
+          <t>5028185</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5157772</t>
+          <t>5172690</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>774702</t>
+          <t>840246</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>592845</t>
+          <t>787282</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>863876</t>
+          <t>894029</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1210995</t>
+          <t>1113074</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1047790</t>
+          <t>1066597</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1664509</t>
+          <t>1169690</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1985697</t>
+          <t>1953320</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1757557</t>
+          <t>1879397</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2464388</t>
+          <t>2023902</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
